--- a/output/pdf_financials_xlsx/HMR.xlsx
+++ b/output/pdf_financials_xlsx/HMR.xlsx
@@ -6168,7 +6168,7 @@
         <v>3.782395</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>6.574847</v>
       </c>
     </row>
     <row r="93">
@@ -7665,16 +7665,16 @@
         <v>0.003074</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.340469</v>
+        <v>0.166183</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>2.059933</v>
+        <v>1.945968</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0124</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0</v>
@@ -7689,7 +7689,7 @@
         <v>0</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="O118" s="3" t="n">
         <v>0.042602</v>
@@ -10920,7 +10920,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -41336,7 +41340,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HMR.xlsx
+++ b/output/pdf_financials_xlsx/HMR.xlsx
@@ -957,19 +957,19 @@
         <v>1.127091</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.227494</v>
+        <v>0.927266</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.498758</v>
+        <v>0.755836</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.421424</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.439789</v>
+        <v>0.5434099999999999</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.543638</v>
+        <v>0.677316</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>1.197153</v>
@@ -1018,7 +1018,7 @@
         <v>-1.127091</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-1.227494</v>
+        <v>-0.927266</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-0.755836</v>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00136</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000153</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1116,13 +1116,13 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.002719</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.013609</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.006298</v>
       </c>
     </row>
     <row r="13">
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.644282</v>
+        <v>-0.642922</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.504785</v>
@@ -2087,7 +2087,7 @@
         <v>-0.579658</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.197</v>
+        <v>-1.197153</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.750718</v>
@@ -2105,13 +2105,13 @@
         <v>-1.236591</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.575182</v>
+        <v>-1.577901</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-3.896676</v>
+        <v>-3.910285</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-9.163511</v>
+        <v>-9.169809000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.644282</v>
+        <v>-0.642922</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.504785</v>
@@ -2209,7 +2209,7 @@
         <v>-0.579658</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.197</v>
+        <v>-1.197153</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.750718</v>
@@ -2227,13 +2227,13 @@
         <v>-1.236591</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.575182</v>
+        <v>-1.577901</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-3.896676</v>
+        <v>-3.910285</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-9.160849000000001</v>
+        <v>-9.167147</v>
       </c>
     </row>
     <row r="30">
@@ -2505,28 +2505,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.01985</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.070753</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.070753</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.035548</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.000629</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000766</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.0009389999999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.008813</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.283356</v>
@@ -2535,28 +2535,28 @@
         <v>0.004877</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.000125</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000113</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.02786</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.099547</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.000489</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.01863</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>1.7079</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.90772</v>
       </c>
     </row>
     <row r="35">
@@ -2627,28 +2627,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.01985</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.070753</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.070753</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.035548</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.000629</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000766</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.0009389999999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.008813</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.283356</v>
@@ -2657,28 +2657,28 @@
         <v>0.004877</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.000125</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000113</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.02786</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.099547</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.000489</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.01863</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>1.7079</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.90772</v>
       </c>
     </row>
     <row r="37">
@@ -3359,28 +3359,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.02585</v>
+        <v>0.006</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.070753</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.04581</v>
+        <v>0.010262</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.004629</v>
+        <v>0.004</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.000766</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.0009389999999999999</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.008813</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.0012</v>
@@ -3392,25 +3392,25 @@
         <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.000613</v>
+        <v>0.0005</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.02836</v>
+        <v>0.0005</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.099547</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.113031</v>
+        <v>0.112542</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.24861</v>
+        <v>0.22998</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.868684</v>
+        <v>0.160784</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>3.69092</v>
+        <v>2.7832</v>
       </c>
     </row>
     <row r="49">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -25260,7 +25260,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -26646,7 +26646,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
@@ -63608,7 +63608,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -71088,7 +71088,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
@@ -72258,7 +72258,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
@@ -74928,7 +74928,7 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
@@ -74952,10 +74952,10 @@
         </is>
       </c>
       <c r="I627" s="5" t="n">
-        <v>-0.927266</v>
+        <v>0.927266</v>
       </c>
       <c r="J627" s="5" t="n">
-        <v>-0.755836</v>
+        <v>0.755836</v>
       </c>
       <c r="K627" t="inlineStr">
         <is>
@@ -81838,7 +81838,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E692" s="5" t="n">

--- a/output/pdf_financials_xlsx/HMR.xlsx
+++ b/output/pdf_financials_xlsx/HMR.xlsx
@@ -4610,10 +4610,10 @@
         <v>0.176588</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.177499</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.49995</v>
       </c>
     </row>
     <row r="68">
@@ -6628,13 +6628,13 @@
         <v>0</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.004956</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.009917</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.027387</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>0.033125</v>
@@ -6649,16 +6649,16 @@
         <v>-0.002267</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>0.004826</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001823</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>0.005113</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001657</v>
       </c>
       <c r="Q101" s="3" t="n">
         <v>-0.007068</v>
@@ -6933,13 +6933,13 @@
         <v>0</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.022893</v>
+        <v>0.027849</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.104243</v>
+        <v>-0.09432599999999999</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.404791</v>
+        <v>0.377404</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>0.462833</v>
@@ -6954,16 +6954,16 @@
         <v>0.357706</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.662864</v>
+        <v>0.66769</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.511996</v>
+        <v>0.510173</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.338963</v>
+        <v>0.344076</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0.077976</v>
+        <v>0.076319</v>
       </c>
       <c r="Q106" s="3" t="n">
         <v>-0.351259</v>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.07711999999999999</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -28946,7 +28946,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -35964,7 +35968,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -40916,7 +40924,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -52492,7 +52504,11 @@
           <t>HST / GST receivable</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
@@ -61068,7 +61084,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E496" s="5" t="n">
         <v>0.07711999999999999</v>
       </c>
